--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_investments_asset_management.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.138</v>
-      </c>
-      <c r="E2">
-        <v>0.0534</v>
+        <v>1.307</v>
       </c>
       <c r="G2">
-        <v>0.02204754601226994</v>
+        <v>0.1394072447859495</v>
       </c>
       <c r="H2">
-        <v>0.02204754601226994</v>
+        <v>0.1394072447859495</v>
       </c>
       <c r="I2">
-        <v>0.6765241564417177</v>
+        <v>0.8570142700329308</v>
       </c>
       <c r="J2">
-        <v>0.6756740737320527</v>
+        <v>0.8570142700329308</v>
       </c>
       <c r="K2">
-        <v>142.4</v>
+        <v>58.919</v>
       </c>
       <c r="L2">
-        <v>3.412576687116565</v>
+        <v>0.3233754116355654</v>
       </c>
       <c r="M2">
-        <v>27.805</v>
+        <v>36.8</v>
       </c>
       <c r="N2">
-        <v>0.08413519728879205</v>
+        <v>0.1223404255319149</v>
       </c>
       <c r="O2">
-        <v>0.1952598314606742</v>
+        <v>0.6245862964408764</v>
       </c>
       <c r="P2">
-        <v>20.835</v>
+        <v>36.8</v>
       </c>
       <c r="Q2">
-        <v>0.06304466230936819</v>
+        <v>0.1223404255319149</v>
       </c>
       <c r="R2">
-        <v>0.146313202247191</v>
+        <v>0.6245862964408764</v>
       </c>
       <c r="S2">
-        <v>6.969999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2506743391476353</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>45.81</v>
+        <v>29.118</v>
       </c>
       <c r="V2">
-        <v>0.1386165577342048</v>
+        <v>0.09680186170212765</v>
       </c>
       <c r="W2">
-        <v>0.2631215469613259</v>
+        <v>0.1692634560906515</v>
       </c>
       <c r="X2">
-        <v>0.09323208345766168</v>
+        <v>0.1362505839018057</v>
       </c>
       <c r="Y2">
-        <v>0.1698894635036643</v>
+        <v>0.03301287218884583</v>
       </c>
       <c r="Z2">
-        <v>0.1012665600481482</v>
+        <v>0.3348501444523674</v>
       </c>
       <c r="AA2">
-        <v>-0.03040135279915267</v>
+        <v>-0.08199884236928419</v>
       </c>
       <c r="AB2">
-        <v>0.09311297890854678</v>
+        <v>0.1361817539618146</v>
       </c>
       <c r="AC2">
-        <v>-0.1234041530768409</v>
+        <v>-0.2181805963310988</v>
       </c>
       <c r="AD2">
-        <v>0.742</v>
+        <v>0.674</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.742</v>
+        <v>0.674</v>
       </c>
       <c r="AG2">
-        <v>-45.068</v>
+        <v>-28.444</v>
       </c>
       <c r="AH2">
-        <v>0.002240189359402455</v>
+        <v>0.002235682015696213</v>
       </c>
       <c r="AI2">
-        <v>0.001257963997138217</v>
+        <v>0.001100111806615361</v>
       </c>
       <c r="AJ2">
-        <v>-0.1579050635572436</v>
+        <v>-0.1044368400182115</v>
       </c>
       <c r="AK2">
-        <v>-0.08284071525204401</v>
+        <v>-0.04874328888675633</v>
       </c>
       <c r="AL2">
-        <v>0.742</v>
+        <v>0.047</v>
       </c>
       <c r="AM2">
-        <v>0.724</v>
+        <v>0.026</v>
       </c>
       <c r="AN2">
-        <v>0.01922279792746114</v>
+        <v>-0.05711864406779661</v>
       </c>
       <c r="AO2">
-        <v>38.04582210242587</v>
+        <v>3322.297872340425</v>
       </c>
       <c r="AP2">
-        <v>-1.167564766839378</v>
+        <v>2.410508474576271</v>
       </c>
       <c r="AQ2">
-        <v>38.99171270718232</v>
+        <v>6005.692307692308</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Livermore Investments Group Limited (AIM:LIV)</t>
+          <t>Symphony International Holdings Limited (LSE:SIHL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +719,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.351</v>
+        <v>1.307</v>
       </c>
       <c r="G3">
-        <v>0.02206235011990408</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.02206235011990408</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9208633093525179</v>
+        <v>0.924259055982437</v>
       </c>
       <c r="J3">
-        <v>0.9173919921654299</v>
+        <v>0.924259055982437</v>
       </c>
       <c r="K3">
-        <v>38.1</v>
+        <v>71.7</v>
       </c>
       <c r="L3">
-        <v>0.9136690647482014</v>
+        <v>0.393523600439078</v>
       </c>
       <c r="M3">
-        <v>14.97</v>
+        <v>12.8</v>
       </c>
       <c r="N3">
-        <v>0.1368372943327239</v>
+        <v>0.05732198835647111</v>
       </c>
       <c r="O3">
-        <v>0.3929133858267716</v>
+        <v>0.1785216178521618</v>
       </c>
       <c r="P3">
-        <v>8</v>
+        <v>12.8</v>
       </c>
       <c r="Q3">
-        <v>0.07312614259597806</v>
+        <v>0.05732198835647111</v>
       </c>
       <c r="R3">
-        <v>0.2099737532808399</v>
+        <v>0.1785216178521618</v>
       </c>
       <c r="S3">
-        <v>6.969999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.4655978623914495</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>19.7</v>
+        <v>9.92</v>
       </c>
       <c r="V3">
-        <v>0.180073126142596</v>
+        <v>0.04442454097626511</v>
       </c>
       <c r="W3">
-        <v>0.2631215469613259</v>
+        <v>0.1692634560906515</v>
       </c>
       <c r="X3">
-        <v>0.09323208345766168</v>
+        <v>0.1361319814789265</v>
       </c>
       <c r="Y3">
-        <v>0.1698894635036643</v>
+        <v>0.03313147461172503</v>
       </c>
       <c r="Z3">
-        <v>0.4938183885178343</v>
+        <v>0.456641604010025</v>
       </c>
       <c r="AA3">
-        <v>0.4530250352102983</v>
+        <v>0.4220551378446115</v>
       </c>
       <c r="AB3">
-        <v>0.09311297890854678</v>
+        <v>0.1361319814789265</v>
       </c>
       <c r="AC3">
-        <v>0.3599120563017515</v>
+        <v>0.285923156365685</v>
       </c>
       <c r="AD3">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-19.276</v>
+        <v>-9.92</v>
       </c>
       <c r="AH3">
-        <v>0.00386072261072261</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.002572440906664078</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2138830944032666</v>
+        <v>-0.04648983034961102</v>
       </c>
       <c r="AK3">
-        <v>-0.1328243433201952</v>
+        <v>-0.02099115493673029</v>
       </c>
       <c r="AL3">
-        <v>0.09</v>
+        <v>0.018</v>
       </c>
       <c r="AM3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>0.01098445595854922</v>
+        <v>0.018</v>
       </c>
       <c r="AO3">
-        <v>426.6666666666667</v>
-      </c>
-      <c r="AP3">
-        <v>-0.4993782383419689</v>
+        <v>9355.555555555557</v>
       </c>
       <c r="AQ3">
-        <v>533.3333333333334</v>
+        <v>9355.555555555557</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symphony International Holdings Limited (LSE:SIHL)</t>
+          <t>Livermore Investments Group Limited (AIM:LIV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,47 +843,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.627</v>
-      </c>
-      <c r="E4">
-        <v>0.0534</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>-355.7142857142857</v>
-      </c>
-      <c r="J4">
-        <v>-355.7142857142857</v>
-      </c>
       <c r="K4">
-        <v>104.7</v>
-      </c>
-      <c r="L4">
-        <v>3739.285714285714</v>
+        <v>-12.4</v>
       </c>
       <c r="M4">
-        <v>12.835</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>0.06025821596244132</v>
+        <v>0.3120936280884265</v>
       </c>
       <c r="O4">
-        <v>0.1225883476599809</v>
+        <v>-1.935483870967742</v>
       </c>
       <c r="P4">
-        <v>12.835</v>
+        <v>24</v>
       </c>
       <c r="Q4">
-        <v>0.06025821596244132</v>
+        <v>0.3120936280884265</v>
       </c>
       <c r="R4">
-        <v>0.1225883476599809</v>
+        <v>-1.935483870967742</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,67 +871,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>24.6</v>
+        <v>18.9</v>
       </c>
       <c r="V4">
-        <v>0.1154929577464789</v>
+        <v>0.2457737321196359</v>
       </c>
       <c r="W4">
-        <v>0.3284190715181932</v>
+        <v>-0.07542579075425791</v>
       </c>
       <c r="X4">
-        <v>0.09300280027768826</v>
+        <v>0.1362505839018057</v>
       </c>
       <c r="Y4">
-        <v>0.235416271240505</v>
+        <v>-0.2116763746560636</v>
       </c>
       <c r="Z4">
-        <v>8.546565043938501e-05</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.03040135279915267</v>
+        <v>-0.08199884236928419</v>
       </c>
       <c r="AB4">
-        <v>0.09300280027768826</v>
+        <v>0.1361817539618146</v>
       </c>
       <c r="AC4">
-        <v>-0.1234041530768409</v>
+        <v>-0.2181805963310988</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="AG4">
-        <v>-24.6</v>
+        <v>-18.774</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.001635811284501337</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.0009682922705685259</v>
       </c>
       <c r="AJ4">
-        <v>-0.1305732484076433</v>
+        <v>-0.3229879916044455</v>
       </c>
       <c r="AK4">
-        <v>-0.06165413533834587</v>
+        <v>-0.1687914696204125</v>
       </c>
       <c r="AL4">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.647</v>
-      </c>
-      <c r="AO4">
-        <v>-15.39412673879444</v>
+        <v>-0.021</v>
+      </c>
+      <c r="AN4">
+        <v>-0.01067796610169492</v>
+      </c>
+      <c r="AP4">
+        <v>1.591016949152542</v>
       </c>
       <c r="AQ4">
-        <v>-15.39412673879444</v>
+        <v>566.6666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anemoi International Limited (LSE:AMOI)</t>
+          <t>Fragrant Prosperity Holdings Limited (LSE:FPP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,7 +954,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-0.4</v>
+        <v>-0.381</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,52 +978,58 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.51</v>
+        <v>0.298</v>
       </c>
       <c r="V5">
-        <v>0.1868811881188119</v>
+        <v>0.4966666666666666</v>
+      </c>
+      <c r="W5">
+        <v>2.015873015873016</v>
       </c>
       <c r="X5">
-        <v>0.09533110286640344</v>
+        <v>0.2022437331063943</v>
+      </c>
+      <c r="Y5">
+        <v>1.813629282766621</v>
       </c>
       <c r="AB5">
-        <v>0.09430383604701181</v>
+        <v>0.1547388055803243</v>
       </c>
       <c r="AD5">
-        <v>0.318</v>
+        <v>0.548</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.318</v>
+        <v>0.548</v>
       </c>
       <c r="AG5">
-        <v>-1.192</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.03786615860919267</v>
+        <v>0.4773519163763066</v>
       </c>
       <c r="AI5">
-        <v>0.2242595204513399</v>
+        <v>14.05128205128204</v>
       </c>
       <c r="AJ5">
-        <v>-0.173054587688734</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="AK5">
-        <v>12.95652173913045</v>
+        <v>-0.9652509652509657</v>
       </c>
       <c r="AL5">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="AM5">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="AO5">
-        <v>-42</v>
+        <v>-12.13793103448276</v>
       </c>
       <c r="AQ5">
-        <v>-42</v>
+        <v>-12.13793103448276</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.307</v>
+        <v>-0.246</v>
+      </c>
+      <c r="E2">
+        <v>-0.386</v>
       </c>
       <c r="G2">
-        <v>0.1394072447859495</v>
+        <v>-4.749498997995992</v>
       </c>
       <c r="H2">
-        <v>0.1394072447859495</v>
+        <v>-4.749498997995992</v>
       </c>
       <c r="I2">
-        <v>0.8570142700329308</v>
+        <v>-1.258517034068136</v>
       </c>
       <c r="J2">
-        <v>0.8570142700329308</v>
+        <v>-1.172590698638657</v>
       </c>
       <c r="K2">
-        <v>58.919</v>
+        <v>-65.05</v>
       </c>
       <c r="L2">
-        <v>0.3233754116355654</v>
+        <v>-13.03607214428858</v>
       </c>
       <c r="M2">
-        <v>36.8</v>
+        <v>12.835</v>
       </c>
       <c r="N2">
-        <v>0.1223404255319149</v>
+        <v>0.04662186705412277</v>
       </c>
       <c r="O2">
-        <v>0.6245862964408764</v>
+        <v>-0.1973097617217525</v>
       </c>
       <c r="P2">
-        <v>36.8</v>
+        <v>12.835</v>
       </c>
       <c r="Q2">
-        <v>0.1223404255319149</v>
+        <v>0.04662186705412277</v>
       </c>
       <c r="R2">
-        <v>0.6245862964408764</v>
+        <v>-0.1973097617217525</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>29.118</v>
+        <v>30.1</v>
       </c>
       <c r="V2">
-        <v>0.09680186170212765</v>
+        <v>0.1093352706138758</v>
       </c>
       <c r="W2">
-        <v>0.1692634560906515</v>
+        <v>-0.06389697090474293</v>
       </c>
       <c r="X2">
-        <v>0.1362505839018057</v>
+        <v>0.08526098482911748</v>
       </c>
       <c r="Y2">
-        <v>0.03301287218884583</v>
+        <v>-0.1491579557338604</v>
       </c>
       <c r="Z2">
-        <v>0.3348501444523674</v>
+        <v>0.008547359910655252</v>
       </c>
       <c r="AA2">
-        <v>-0.08199884236928419</v>
+        <v>-0.001166822893620514</v>
       </c>
       <c r="AB2">
-        <v>0.1361817539618146</v>
+        <v>0.08475130096649387</v>
       </c>
       <c r="AC2">
-        <v>-0.2181805963310988</v>
+        <v>-0.08591812386011438</v>
       </c>
       <c r="AD2">
-        <v>0.674</v>
+        <v>2.03</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.674</v>
+        <v>2.03</v>
       </c>
       <c r="AG2">
-        <v>-28.444</v>
+        <v>-28.07</v>
       </c>
       <c r="AH2">
-        <v>0.002235682015696213</v>
+        <v>0.007319799516821116</v>
       </c>
       <c r="AI2">
-        <v>0.001100111806615361</v>
+        <v>0.003780753543292422</v>
       </c>
       <c r="AJ2">
-        <v>-0.1044368400182115</v>
+        <v>-0.1135380010516523</v>
       </c>
       <c r="AK2">
-        <v>-0.04874328888675633</v>
+        <v>-0.05538346191030524</v>
       </c>
       <c r="AL2">
-        <v>0.047</v>
+        <v>0.035</v>
       </c>
       <c r="AM2">
-        <v>0.026</v>
+        <v>-14.741</v>
       </c>
       <c r="AN2">
-        <v>-0.05711864406779661</v>
+        <v>0.9950980392156862</v>
       </c>
       <c r="AO2">
-        <v>3322.297872340425</v>
+        <v>-179.4285714285714</v>
       </c>
       <c r="AP2">
-        <v>2.410508474576271</v>
+        <v>-13.75980392156863</v>
       </c>
       <c r="AQ2">
-        <v>6005.692307692308</v>
+        <v>0.4260226578929517</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Symphony International Holdings Limited (LSE:SIHL)</t>
+          <t>Livermore Investments Group Limited (AIM:LIV)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,112 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.307</v>
+        <v>-0.246</v>
+      </c>
+      <c r="E3">
+        <v>-0.386</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-4.749498997995992</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-4.749498997995992</v>
       </c>
       <c r="I3">
-        <v>0.924259055982437</v>
+        <v>0.3887775551102204</v>
       </c>
       <c r="J3">
-        <v>0.924259055982437</v>
+        <v>0.3356893096537903</v>
       </c>
       <c r="K3">
-        <v>71.7</v>
+        <v>1.25</v>
       </c>
       <c r="L3">
-        <v>0.393523600439078</v>
+        <v>0.250501002004008</v>
       </c>
       <c r="M3">
-        <v>12.8</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05732198835647111</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1785216178521618</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>12.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.05732198835647111</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1785216178521618</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>9.92</v>
+        <v>13.3</v>
       </c>
       <c r="V3">
-        <v>0.04442454097626511</v>
+        <v>0.2003012048192771</v>
       </c>
       <c r="W3">
-        <v>0.1692634560906515</v>
+        <v>0.009615384615384616</v>
       </c>
       <c r="X3">
-        <v>0.1361319814789265</v>
+        <v>0.08572504119027242</v>
       </c>
       <c r="Y3">
-        <v>0.03313147461172503</v>
+        <v>-0.0761096565748878</v>
       </c>
       <c r="Z3">
-        <v>0.456641604010025</v>
+        <v>0.04486361102619892</v>
       </c>
       <c r="AA3">
-        <v>0.4220551378446115</v>
+        <v>0.01506023461396089</v>
       </c>
       <c r="AB3">
-        <v>0.1361319814789265</v>
+        <v>0.08470567346502519</v>
       </c>
       <c r="AC3">
-        <v>0.285923156365685</v>
+        <v>-0.06964543885106431</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG3">
-        <v>-9.92</v>
+        <v>-11.27</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.02966535145404062</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01519119958093242</v>
       </c>
       <c r="AJ3">
-        <v>-0.04648983034961102</v>
+        <v>-0.2044259024124796</v>
       </c>
       <c r="AK3">
-        <v>-0.02099115493673029</v>
+        <v>-0.09365910413030833</v>
       </c>
       <c r="AL3">
-        <v>0.018</v>
+        <v>0.035</v>
       </c>
       <c r="AM3">
-        <v>0.018</v>
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>0.9950980392156862</v>
       </c>
       <c r="AO3">
-        <v>9355.555555555557</v>
+        <v>55.42857142857142</v>
+      </c>
+      <c r="AP3">
+        <v>-5.524509803921569</v>
       </c>
       <c r="AQ3">
-        <v>9355.555555555557</v>
+        <v>-47.31707317073171</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Livermore Investments Group Limited (AIM:LIV)</t>
+          <t>Symphony International Holdings Limited (LSE:SIHL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +853,25 @@
         </is>
       </c>
       <c r="K4">
-        <v>-12.4</v>
+        <v>-66.3</v>
       </c>
       <c r="M4">
-        <v>24</v>
+        <v>12.835</v>
       </c>
       <c r="N4">
-        <v>0.3120936280884265</v>
+        <v>0.06144088080421255</v>
       </c>
       <c r="O4">
-        <v>-1.935483870967742</v>
+        <v>-0.1935897435897436</v>
       </c>
       <c r="P4">
-        <v>24</v>
+        <v>12.835</v>
       </c>
       <c r="Q4">
-        <v>0.3120936280884265</v>
+        <v>0.06144088080421255</v>
       </c>
       <c r="R4">
-        <v>-1.935483870967742</v>
+        <v>-0.1935897435897436</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -871,165 +880,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>18.9</v>
+        <v>16.8</v>
       </c>
       <c r="V4">
-        <v>0.2457737321196359</v>
+        <v>0.08042125418860699</v>
       </c>
       <c r="W4">
-        <v>-0.07542579075425791</v>
+        <v>-0.1374093264248705</v>
       </c>
       <c r="X4">
-        <v>0.1362505839018057</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="Y4">
-        <v>-0.2116763746560636</v>
+        <v>-0.222206254892833</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.08199884236928419</v>
+        <v>-0.01739388040120192</v>
       </c>
       <c r="AB4">
-        <v>0.1361817539618146</v>
+        <v>0.08479692846796255</v>
       </c>
       <c r="AC4">
-        <v>-0.2181805963310988</v>
+        <v>-0.1021908088691645</v>
       </c>
       <c r="AD4">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-18.774</v>
+        <v>-16.8</v>
       </c>
       <c r="AH4">
-        <v>0.001635811284501337</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.0009682922705685259</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.3229879916044455</v>
+        <v>-0.08745445080687143</v>
       </c>
       <c r="AK4">
-        <v>-0.1687914696204125</v>
+        <v>-0.04346701164294955</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.021</v>
-      </c>
-      <c r="AN4">
-        <v>-0.01067796610169492</v>
-      </c>
-      <c r="AP4">
-        <v>1.591016949152542</v>
+        <v>-14.7</v>
       </c>
       <c r="AQ4">
-        <v>566.6666666666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>British Virgin Islands</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fragrant Prosperity Holdings Limited (LSE:FPP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>-0.381</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.298</v>
-      </c>
-      <c r="V5">
-        <v>0.4966666666666666</v>
-      </c>
-      <c r="W5">
-        <v>2.015873015873016</v>
-      </c>
-      <c r="X5">
-        <v>0.2022437331063943</v>
-      </c>
-      <c r="Y5">
-        <v>1.813629282766621</v>
-      </c>
-      <c r="AB5">
-        <v>0.1547388055803243</v>
-      </c>
-      <c r="AD5">
-        <v>0.548</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0.548</v>
-      </c>
-      <c r="AG5">
-        <v>0.2500000000000001</v>
-      </c>
-      <c r="AH5">
-        <v>0.4773519163763066</v>
-      </c>
-      <c r="AI5">
-        <v>14.05128205128204</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="AK5">
-        <v>-0.9652509652509657</v>
-      </c>
-      <c r="AL5">
-        <v>0.029</v>
-      </c>
-      <c r="AM5">
-        <v>0.029</v>
-      </c>
-      <c r="AO5">
-        <v>-12.13793103448276</v>
-      </c>
-      <c r="AQ5">
-        <v>-12.13793103448276</v>
+        <v>0.5591836734693878</v>
       </c>
     </row>
   </sheetData>
